--- a/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt2_rubricas.xlsx
@@ -1608,13 +1608,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EFCC1B8-79C5-4795-8068-AF1E36C2A1F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDDAB9C1-8200-40FB-91DA-A3EC1EB9B839}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83C8848-620A-4C92-95CC-010D0C96CF71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D24FA41-B356-4548-91E2-EB5DBF429FF8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9969A7FE-8B4A-4739-84D2-22860D1D0802}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34EB6803-6176-4B70-9E55-120502DC7E69}"/>
 </file>